--- a/artfynd/A 44728-2025 artfynd.xlsx
+++ b/artfynd/A 44728-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74517426</v>
       </c>
       <c r="B2" t="n">
-        <v>97321</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99616</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>399707.2574404679</v>
+        <v>399707</v>
       </c>
       <c r="R2" t="n">
-        <v>6344467.416634936</v>
+        <v>6344467</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>2003-09-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2003-09-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 44728-2025 artfynd.xlsx
+++ b/artfynd/A 44728-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74517426</v>
       </c>
       <c r="B2" t="n">
-        <v>99616</v>
+        <v>99621</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44728-2025 artfynd.xlsx
+++ b/artfynd/A 44728-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74517426</v>
       </c>
       <c r="B2" t="n">
-        <v>99621</v>
+        <v>99622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44728-2025 artfynd.xlsx
+++ b/artfynd/A 44728-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74517426</v>
       </c>
       <c r="B2" t="n">
-        <v>99622</v>
+        <v>99649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44728-2025 artfynd.xlsx
+++ b/artfynd/A 44728-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74517426</v>
       </c>
       <c r="B2" t="n">
-        <v>99649</v>
+        <v>99655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44728-2025 artfynd.xlsx
+++ b/artfynd/A 44728-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74517426</v>
       </c>
       <c r="B2" t="n">
-        <v>99655</v>
+        <v>99662</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44728-2025 artfynd.xlsx
+++ b/artfynd/A 44728-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74517426</v>
       </c>
       <c r="B2" t="n">
-        <v>99662</v>
+        <v>99666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44728-2025 artfynd.xlsx
+++ b/artfynd/A 44728-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74517426</v>
       </c>
       <c r="B2" t="n">
-        <v>99666</v>
+        <v>99673</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44728-2025 artfynd.xlsx
+++ b/artfynd/A 44728-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74517426</v>
       </c>
       <c r="B2" t="n">
-        <v>99676</v>
+        <v>99681</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44728-2025 artfynd.xlsx
+++ b/artfynd/A 44728-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74517426</v>
       </c>
       <c r="B2" t="n">
-        <v>99681</v>
+        <v>99689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44728-2025 artfynd.xlsx
+++ b/artfynd/A 44728-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74517426</v>
       </c>
       <c r="B2" t="n">
-        <v>99689</v>
+        <v>99699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44728-2025 artfynd.xlsx
+++ b/artfynd/A 44728-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74517426</v>
+        <v>74517422</v>
       </c>
       <c r="B2" t="n">
-        <v>99699</v>
+        <v>100157</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Atlasruta 5D9a, Sm</t>
+          <t>Yxasjöns SV-vik, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -740,17 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2003-09-12</t>
+          <t>1989-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2003-09-12</t>
+          <t>1989-12-31</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5D9a 2810. SOM: Isolepis fluitans. LEG: Kerstin Johansson. KOM: 0,5 m²</t>
+          <t>Smålands flora 2007: KOO: 5D9a 2810. SOM: Isolepis fluitans. LEG: Kerstin Johansson</t>
         </is>
       </c>
       <c r="AD2" t="b">
